--- a/public/templates/en/impact-assessment.xlsx
+++ b/public/templates/en/impact-assessment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -748,13 +748,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Prioritisation for AI (optional)</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>How heavily is the service used?</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>Low: limited use, infrequent transactions; Medium; High: wide use, repeated transactions</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -765,13 +765,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Prioritisation for AI (optional)</v>
       </c>
       <c r="B22" t="str">
-        <v>Resulting tier</v>
+        <v>How complex is the service to deliver or transform?</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>Low: simple, standard, repeatable; Medium; High: multi-entity, variable, heavily governed</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -782,13 +782,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Prioritisation for AI (optional)</v>
       </c>
       <c r="B23" t="str">
-        <v>Reasons</v>
+        <v>How ready is the service for AI?</v>
       </c>
       <c r="C23" t="str">
-        <v/>
+        <v>Low: manual, fragmented, unclear; Medium; High: structured, digital, integrated</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -802,7 +802,7 @@
         <v/>
       </c>
       <c r="B24" t="str">
-        <v>Sign-off</v>
+        <v/>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>Prepared by</v>
+        <v>Resulting tier</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>Reviewed by</v>
+        <v>Reasons</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>Decision</v>
+        <v>Sign-off</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -870,21 +870,72 @@
         <v/>
       </c>
       <c r="B28" t="str">
+        <v>Prepared by</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v/>
+      </c>
+      <c r="B29" t="str">
+        <v>Reviewed by</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+      <c r="B30" t="str">
+        <v>Decision</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v/>
+      </c>
+      <c r="B31" t="str">
         <v>Date</v>
       </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/en/impact-assessment.xlsx
+++ b/public/templates/en/impact-assessment.xlsx
@@ -754,7 +754,7 @@
         <v>How heavily is the service used?</v>
       </c>
       <c r="C21" t="str">
-        <v>Low: limited use, infrequent transactions; Medium; High: wide use, repeated transactions</v>
+        <v>Heavy: wide use, repeated transactions; Moderate; Light: limited use, infrequent transactions</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -771,7 +771,7 @@
         <v>How complex is the service to deliver or transform?</v>
       </c>
       <c r="C22" t="str">
-        <v>Low: simple, standard, repeatable; Medium; High: multi-entity, variable, heavily governed</v>
+        <v>Simple: standard, repeatable; Moderately complex; Very complex: multi-entity, variable, heavily governed</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -788,7 +788,7 @@
         <v>How ready is the service for AI?</v>
       </c>
       <c r="C23" t="str">
-        <v>Low: manual, fragmented, unclear; Medium; High: structured, digital, integrated</v>
+        <v>Ready (digital, integrated); Partly ready; Not ready (manual, fragmented)</v>
       </c>
       <c r="D23" t="str">
         <v/>

--- a/public/templates/en/impact-assessment.xlsx
+++ b/public/templates/en/impact-assessment.xlsx
@@ -748,7 +748,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Prioritisation for AI (optional)</v>
+        <v>Prioritisation for AI</v>
       </c>
       <c r="B21" t="str">
         <v>How heavily is the service used?</v>
@@ -765,7 +765,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Prioritisation for AI (optional)</v>
+        <v>Prioritisation for AI</v>
       </c>
       <c r="B22" t="str">
         <v>How complex is the service to deliver or transform?</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Prioritisation for AI (optional)</v>
+        <v>Prioritisation for AI</v>
       </c>
       <c r="B23" t="str">
         <v>How ready is the service for AI?</v>

--- a/public/templates/en/impact-assessment.xlsx
+++ b/public/templates/en/impact-assessment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" customWidth="1"/>
@@ -442,13 +442,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Quick check</v>
+        <v>Scope</v>
       </c>
       <c r="B3" t="str">
-        <v>What does the AI's output influence?</v>
+        <v>Does the solution use AI when it runs?</v>
       </c>
       <c r="C3" t="str">
-        <v>Internal productivity only (drafts, summaries, search) (0); Information given to the public or customers (5); Recommendations to staff about specific people (15); Decisions about people's rights, benefits, access to services or money (25); Social scoring, manipulation, or real-time biometric surveillance of the public (0)</v>
+        <v>Yes: it uses an AI model or AI service when it runs; No: AI was only used to build it, or not at all</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -462,10 +462,10 @@
         <v>Quick check</v>
       </c>
       <c r="B4" t="str">
-        <v>What data does it use?</v>
+        <v>What does the AI's output influence?</v>
       </c>
       <c r="C4" t="str">
-        <v>No data about people, or public data only (0); Internal business data, no personal data (3); Personal data (10); Sensitive personal data (18)</v>
+        <v>Internal productivity only (drafts, summaries, search) (0); Information given to the public or customers (5); Recommendations to staff about specific people (15); Decisions about people's rights, benefits, access to services or money (25); Social scoring, manipulation, or real-time biometric surveillance of the public (0)</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -479,10 +479,10 @@
         <v>Quick check</v>
       </c>
       <c r="B5" t="str">
-        <v>Who could be affected?</v>
+        <v>What data does it use?</v>
       </c>
       <c r="C5" t="str">
-        <v>Employees only (3); Customers or the public (8); Vulnerable groups (children, elderly, people with disabilities) (15)</v>
+        <v>No data about people, or public data only (0); Internal business data, no personal data (3); Personal data (10); Sensitive personal data (18)</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -496,10 +496,10 @@
         <v>Quick check</v>
       </c>
       <c r="B6" t="str">
-        <v>What kind of AI is it?</v>
+        <v>Who could be affected?</v>
       </c>
       <c r="C6" t="str">
-        <v>Predictive (scores, classifies, forecasts) (5); Generative (writes text, images or answers) (5); Agentic (plans and takes actions) (10)</v>
+        <v>Employees only (3); Customers or the public (8); Vulnerable groups (children, elderly, people with disabilities) (15)</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -513,10 +513,10 @@
         <v>Quick check</v>
       </c>
       <c r="B7" t="str">
-        <v>How much does it act on its own?</v>
+        <v>What kind of AI is it?</v>
       </c>
       <c r="C7" t="str">
-        <v>It only suggests; a person decides and acts (0); It acts only after a person approves (5); It acts on its own; people monitor (15); Fully autonomous, no routine human involvement (25)</v>
+        <v>Predictive (scores, classifies, forecasts) (5); Generative (writes text, images or answers) (5); Agentic (plans and takes actions) (10)</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -530,10 +530,10 @@
         <v>Quick check</v>
       </c>
       <c r="B8" t="str">
-        <v>How is its work reviewed by people?</v>
+        <v>How much does it act on its own?</v>
       </c>
       <c r="C8" t="str">
-        <v>A person reviews every output (0); People review samples or exceptions (5); Only when someone complains (12); No routine review (20)</v>
+        <v>It only suggests; a person decides and acts (0); It acts only after a person approves (5); It acts on its own; people monitor (15); Fully autonomous, no routine human involvement (25)</v>
       </c>
       <c r="D8" t="str">
         <v/>
@@ -547,10 +547,10 @@
         <v>Quick check</v>
       </c>
       <c r="B9" t="str">
-        <v>What can it change in other systems?</v>
+        <v>How is its work reviewed by people?</v>
       </c>
       <c r="C9" t="str">
-        <v>Nothing: no access, or read-only (0); Writes to internal, non-critical tools (8); Writes to systems of record, makes payments, or sends external messages (15)</v>
+        <v>A person reviews every output (0); People review samples or exceptions (5); Only when someone complains (12); No routine review (20)</v>
       </c>
       <c r="D9" t="str">
         <v/>
@@ -564,10 +564,10 @@
         <v>Quick check</v>
       </c>
       <c r="B10" t="str">
-        <v>If it gets something wrong, can the result be undone?</v>
+        <v>What can it change in other systems?</v>
       </c>
       <c r="C10" t="str">
-        <v>Yes, easily (0); Yes, with effort (6); No, or only with lasting harm (15)</v>
+        <v>Nothing: no access, or read-only (0); Writes to internal, non-critical tools (8); Writes to systems of record, makes payments, or sends external messages (15)</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -578,13 +578,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Deep-dive</v>
+        <v>Quick check</v>
       </c>
       <c r="B11" t="str">
-        <v>How many people does it affect per month?</v>
+        <v>If it gets something wrong, can the result be undone?</v>
       </c>
       <c r="C11" t="str">
-        <v>Fewer than 1,000 (0); 1,000 to 100,000 (4); More than 100,000 (8)</v>
+        <v>Yes, easily (0); Yes, with effort (6); No, or only with lasting harm (15)</v>
       </c>
       <c r="D11" t="str">
         <v/>
@@ -598,10 +598,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B12" t="str">
-        <v>Can you explain an individual result to the person affected?</v>
+        <v>How many people does it affect per month?</v>
       </c>
       <c r="C12" t="str">
-        <v>Yes, in plain language (0); Partly (4); No (8)</v>
+        <v>Fewer than 1,000 (0); 1,000 to 100,000 (4); More than 100,000 (8)</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -615,10 +615,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B13" t="str">
-        <v>Does it rely on a third-party model or service?</v>
+        <v>Can you explain an individual result to the person affected?</v>
       </c>
       <c r="C13" t="str">
-        <v>No, built and hosted in-house (0); Yes, hosted in-country under our control (3); Yes, an external service outside our control (6)</v>
+        <v>Yes, in plain language (0); Partly (4); No (8)</v>
       </c>
       <c r="D13" t="str">
         <v/>
@@ -632,10 +632,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B14" t="str">
-        <v>Does data leave the country?</v>
+        <v>Does it rely on a third-party model or service?</v>
       </c>
       <c r="C14" t="str">
-        <v>No (0); Not sure (4); Yes (6)</v>
+        <v>No, built and hosted in-house (0); Yes, hosted in-country under our control (3); Yes, an external service outside our control (6)</v>
       </c>
       <c r="D14" t="str">
         <v/>
@@ -649,10 +649,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B15" t="str">
-        <v>Has it been tested for unfair results across groups?</v>
+        <v>Does data leave the country?</v>
       </c>
       <c r="C15" t="str">
-        <v>Yes, with documented results (0); Planned, not done yet (4); No (8)</v>
+        <v>No (0); Not sure (4); Yes (6)</v>
       </c>
       <c r="D15" t="str">
         <v/>
@@ -666,10 +666,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B16" t="str">
-        <v>Has it been tested against misuse and attacks (e.g. prompt injection)?</v>
+        <v>Has it been tested for unfair results across groups?</v>
       </c>
       <c r="C16" t="str">
-        <v>Yes (0); Planned (4); No (8)</v>
+        <v>Yes, with documented results (0); Planned, not done yet (4); No (8)</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -683,10 +683,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B17" t="str">
-        <v>Is its performance monitored after launch?</v>
+        <v>Has it been tested against misuse and attacks (e.g. prompt injection)?</v>
       </c>
       <c r="C17" t="str">
-        <v>Yes, with defined metrics and owners (0); Ad hoc (4); No (8)</v>
+        <v>Yes (0); Planned (4); No (8)</v>
       </c>
       <c r="D17" t="str">
         <v/>
@@ -700,10 +700,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B18" t="str">
-        <v>Is there a way to stop it and handle incidents?</v>
+        <v>Is its performance monitored after launch?</v>
       </c>
       <c r="C18" t="str">
-        <v>Yes, documented and tested (0); Partly (4); No (8)</v>
+        <v>Yes, with defined metrics and owners (0); Ad hoc (4); No (8)</v>
       </c>
       <c r="D18" t="str">
         <v/>
@@ -717,10 +717,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B19" t="str">
-        <v>Is it used in a regulated domain?</v>
+        <v>Is there a way to stop it and handle incidents?</v>
       </c>
       <c r="C19" t="str">
-        <v>No (0); Yes (6)</v>
+        <v>Yes, documented and tested (0); Partly (4); No (8)</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -734,10 +734,10 @@
         <v>Deep-dive</v>
       </c>
       <c r="B20" t="str">
-        <v>Are people told they are dealing with AI?</v>
+        <v>Is it used in a regulated domain?</v>
       </c>
       <c r="C20" t="str">
-        <v>Yes, clearly (0); No (5)</v>
+        <v>No (0); Yes (6)</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -748,13 +748,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Prioritisation for AI</v>
+        <v>Deep-dive</v>
       </c>
       <c r="B21" t="str">
-        <v>How heavily is the service used?</v>
+        <v>Are people told they are dealing with AI?</v>
       </c>
       <c r="C21" t="str">
-        <v>Heavy: wide use, repeated transactions; Moderate; Light: limited use, infrequent transactions</v>
+        <v>Yes, clearly (0); No (5)</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -768,10 +768,10 @@
         <v>Prioritisation for AI</v>
       </c>
       <c r="B22" t="str">
-        <v>How complex is the service to deliver or transform?</v>
+        <v>How heavily is the service used?</v>
       </c>
       <c r="C22" t="str">
-        <v>Simple: standard, repeatable; Moderately complex; Very complex: multi-entity, variable, heavily governed</v>
+        <v>Heavy: wide use, repeated transactions; Moderate; Light: limited use, infrequent transactions</v>
       </c>
       <c r="D22" t="str">
         <v/>
@@ -785,10 +785,10 @@
         <v>Prioritisation for AI</v>
       </c>
       <c r="B23" t="str">
-        <v>How ready is the service for AI?</v>
+        <v>How complex is the service to deliver or transform?</v>
       </c>
       <c r="C23" t="str">
-        <v>Ready (digital, integrated); Partly ready; Not ready (manual, fragmented)</v>
+        <v>Simple: standard, repeatable; Moderately complex; Very complex: multi-entity, variable, heavily governed</v>
       </c>
       <c r="D23" t="str">
         <v/>
@@ -799,13 +799,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Prioritisation for AI</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>How ready is the service for AI?</v>
       </c>
       <c r="C24" t="str">
-        <v/>
+        <v>Ready (digital, integrated); Partly ready; Not ready (manual, fragmented)</v>
       </c>
       <c r="D24" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>Resulting tier</v>
+        <v/>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -836,7 +836,7 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>Reasons</v>
+        <v>Resulting tier</v>
       </c>
       <c r="C26" t="str">
         <v/>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>Sign-off</v>
+        <v>Reasons</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -870,7 +870,7 @@
         <v/>
       </c>
       <c r="B28" t="str">
-        <v>Prepared by</v>
+        <v>Sign-off</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -887,7 +887,7 @@
         <v/>
       </c>
       <c r="B29" t="str">
-        <v>Reviewed by</v>
+        <v>Prepared by</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -904,7 +904,7 @@
         <v/>
       </c>
       <c r="B30" t="str">
-        <v>Decision</v>
+        <v>Reviewed by</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -921,21 +921,38 @@
         <v/>
       </c>
       <c r="B31" t="str">
+        <v>Decision</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v/>
+      </c>
+      <c r="B32" t="str">
         <v>Date</v>
       </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/en/impact-assessment.xlsx
+++ b/public/templates/en/impact-assessment.xlsx
@@ -465,7 +465,7 @@
         <v>What does the AI's output influence?</v>
       </c>
       <c r="C4" t="str">
-        <v>Internal productivity only (drafts, summaries, search) (0); Information given to the public or customers (5); Recommendations to staff about specific people (15); Decisions about people's rights, benefits, access to services or money (25); Social scoring, manipulation, or real-time biometric surveillance of the public (0)</v>
+        <v>Internal productivity only (drafts, summaries, search) (0); Information given to the public or customers (5); Recommendations to staff about specific people (15); Decisions about people's rights, benefits, access to services or money (25); High-stakes decisions or positions about other companies (claims, contract positions, commercial or credit decisions on firms) (20); Social scoring, manipulation, or real-time biometric surveillance of the public (0)</v>
       </c>
       <c r="D4" t="str">
         <v/>
